--- a/request_forms/027_medical_requisition_form--request_forms.xlsx
+++ b/request_forms/027_medical_requisition_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'medical_cart'}</t>
+          <t>medical_cart</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Medical Cart'}</t>
+          <t>Medical Cart</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'iv_stand'}</t>
+          <t>iv_stand</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'IV Stand'}</t>
+          <t>IV Stand</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'blood_pressure_monitor'}</t>
+          <t>blood_pressure_monitor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Blood Pressure Monitor'}</t>
+          <t>Blood Pressure Monitor</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'defibrillator'}</t>
+          <t>defibrillator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Defibrillator'}</t>
+          <t>Defibrillator</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'oxygen_tank'}</t>
+          <t>oxygen_tank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Oxygen Tank'}</t>
+          <t>Oxygen Tank</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'surgical_light'}</t>
+          <t>surgical_light</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Surgical Light'}</t>
+          <t>Surgical Light</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'gloves'}</t>
+          <t>gloves</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Gloves'}</t>
+          <t>Gloves</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'gown'}</t>
+          <t>gown</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Gown'}</t>
+          <t>Gown</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'face_mask'}</t>
+          <t>face_mask</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Face Mask'}</t>
+          <t>Face Mask</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'surgical_gauze'}</t>
+          <t>surgical_gauze</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Surgical Gauze'}</t>
+          <t>Surgical Gauze</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'aspirin'}</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Aspirin'}</t>
+          <t>Aspirin</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'epinephrine'}</t>
+          <t>epinephrine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Epinephrine'}</t>
+          <t>Epinephrine</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'fentanyl'}</t>
+          <t>fentanyl</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Fentanyl'}</t>
+          <t>Fentanyl</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'hydralazine'}</t>
+          <t>hydralazine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Hydralazine'}</t>
+          <t>Hydralazine</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'metoprolol'}</t>
+          <t>metoprolol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Metoprolol'}</t>
+          <t>Metoprolol</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'morphine'}</t>
+          <t>morphine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Morphine'}</t>
+          <t>Morphine</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'naloxone'}</t>
+          <t>naloxone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Naloxone'}</t>
+          <t>Naloxone</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'oxytocin'}</t>
+          <t>oxytocin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Oxytocin'}</t>
+          <t>Oxytocin</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'sulfamylon'}</t>
+          <t>sulfamylon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Sulfamylon'}</t>
+          <t>Sulfamylon</t>
         </is>
       </c>
     </row>
